--- a/resources/templates/system/deregistration_contract.xlsx
+++ b/resources/templates/system/deregistration_contract.xlsx
@@ -3360,385 +3360,7 @@
     <col width="19" customWidth="1" style="1" min="5" max="5"/>
     <col width="9" customWidth="1" style="1" min="6" max="7"/>
     <col width="16.25" customWidth="1" style="1" min="8" max="8"/>
-    <col width="9" customWidth="1" style="1" min="9" max="256"/>
-    <col width="20.25" customWidth="1" style="1" min="257" max="257"/>
-    <col width="18.625" customWidth="1" style="1" min="258" max="258"/>
-    <col width="16.25" customWidth="1" style="1" min="259" max="259"/>
-    <col width="19.875" customWidth="1" style="1" min="260" max="260"/>
-    <col width="19" customWidth="1" style="1" min="261" max="261"/>
-    <col width="9" customWidth="1" style="1" min="262" max="512"/>
-    <col width="20.25" customWidth="1" style="1" min="513" max="513"/>
-    <col width="18.625" customWidth="1" style="1" min="514" max="514"/>
-    <col width="16.25" customWidth="1" style="1" min="515" max="515"/>
-    <col width="19.875" customWidth="1" style="1" min="516" max="516"/>
-    <col width="19" customWidth="1" style="1" min="517" max="517"/>
-    <col width="9" customWidth="1" style="1" min="518" max="768"/>
-    <col width="20.25" customWidth="1" style="1" min="769" max="769"/>
-    <col width="18.625" customWidth="1" style="1" min="770" max="770"/>
-    <col width="16.25" customWidth="1" style="1" min="771" max="771"/>
-    <col width="19.875" customWidth="1" style="1" min="772" max="772"/>
-    <col width="19" customWidth="1" style="1" min="773" max="773"/>
-    <col width="9" customWidth="1" style="1" min="774" max="1024"/>
-    <col width="20.25" customWidth="1" style="1" min="1025" max="1025"/>
-    <col width="18.625" customWidth="1" style="1" min="1026" max="1026"/>
-    <col width="16.25" customWidth="1" style="1" min="1027" max="1027"/>
-    <col width="19.875" customWidth="1" style="1" min="1028" max="1028"/>
-    <col width="19" customWidth="1" style="1" min="1029" max="1029"/>
-    <col width="9" customWidth="1" style="1" min="1030" max="1280"/>
-    <col width="20.25" customWidth="1" style="1" min="1281" max="1281"/>
-    <col width="18.625" customWidth="1" style="1" min="1282" max="1282"/>
-    <col width="16.25" customWidth="1" style="1" min="1283" max="1283"/>
-    <col width="19.875" customWidth="1" style="1" min="1284" max="1284"/>
-    <col width="19" customWidth="1" style="1" min="1285" max="1285"/>
-    <col width="9" customWidth="1" style="1" min="1286" max="1536"/>
-    <col width="20.25" customWidth="1" style="1" min="1537" max="1537"/>
-    <col width="18.625" customWidth="1" style="1" min="1538" max="1538"/>
-    <col width="16.25" customWidth="1" style="1" min="1539" max="1539"/>
-    <col width="19.875" customWidth="1" style="1" min="1540" max="1540"/>
-    <col width="19" customWidth="1" style="1" min="1541" max="1541"/>
-    <col width="9" customWidth="1" style="1" min="1542" max="1792"/>
-    <col width="20.25" customWidth="1" style="1" min="1793" max="1793"/>
-    <col width="18.625" customWidth="1" style="1" min="1794" max="1794"/>
-    <col width="16.25" customWidth="1" style="1" min="1795" max="1795"/>
-    <col width="19.875" customWidth="1" style="1" min="1796" max="1796"/>
-    <col width="19" customWidth="1" style="1" min="1797" max="1797"/>
-    <col width="9" customWidth="1" style="1" min="1798" max="2048"/>
-    <col width="20.25" customWidth="1" style="1" min="2049" max="2049"/>
-    <col width="18.625" customWidth="1" style="1" min="2050" max="2050"/>
-    <col width="16.25" customWidth="1" style="1" min="2051" max="2051"/>
-    <col width="19.875" customWidth="1" style="1" min="2052" max="2052"/>
-    <col width="19" customWidth="1" style="1" min="2053" max="2053"/>
-    <col width="9" customWidth="1" style="1" min="2054" max="2304"/>
-    <col width="20.25" customWidth="1" style="1" min="2305" max="2305"/>
-    <col width="18.625" customWidth="1" style="1" min="2306" max="2306"/>
-    <col width="16.25" customWidth="1" style="1" min="2307" max="2307"/>
-    <col width="19.875" customWidth="1" style="1" min="2308" max="2308"/>
-    <col width="19" customWidth="1" style="1" min="2309" max="2309"/>
-    <col width="9" customWidth="1" style="1" min="2310" max="2560"/>
-    <col width="20.25" customWidth="1" style="1" min="2561" max="2561"/>
-    <col width="18.625" customWidth="1" style="1" min="2562" max="2562"/>
-    <col width="16.25" customWidth="1" style="1" min="2563" max="2563"/>
-    <col width="19.875" customWidth="1" style="1" min="2564" max="2564"/>
-    <col width="19" customWidth="1" style="1" min="2565" max="2565"/>
-    <col width="9" customWidth="1" style="1" min="2566" max="2816"/>
-    <col width="20.25" customWidth="1" style="1" min="2817" max="2817"/>
-    <col width="18.625" customWidth="1" style="1" min="2818" max="2818"/>
-    <col width="16.25" customWidth="1" style="1" min="2819" max="2819"/>
-    <col width="19.875" customWidth="1" style="1" min="2820" max="2820"/>
-    <col width="19" customWidth="1" style="1" min="2821" max="2821"/>
-    <col width="9" customWidth="1" style="1" min="2822" max="3072"/>
-    <col width="20.25" customWidth="1" style="1" min="3073" max="3073"/>
-    <col width="18.625" customWidth="1" style="1" min="3074" max="3074"/>
-    <col width="16.25" customWidth="1" style="1" min="3075" max="3075"/>
-    <col width="19.875" customWidth="1" style="1" min="3076" max="3076"/>
-    <col width="19" customWidth="1" style="1" min="3077" max="3077"/>
-    <col width="9" customWidth="1" style="1" min="3078" max="3328"/>
-    <col width="20.25" customWidth="1" style="1" min="3329" max="3329"/>
-    <col width="18.625" customWidth="1" style="1" min="3330" max="3330"/>
-    <col width="16.25" customWidth="1" style="1" min="3331" max="3331"/>
-    <col width="19.875" customWidth="1" style="1" min="3332" max="3332"/>
-    <col width="19" customWidth="1" style="1" min="3333" max="3333"/>
-    <col width="9" customWidth="1" style="1" min="3334" max="3584"/>
-    <col width="20.25" customWidth="1" style="1" min="3585" max="3585"/>
-    <col width="18.625" customWidth="1" style="1" min="3586" max="3586"/>
-    <col width="16.25" customWidth="1" style="1" min="3587" max="3587"/>
-    <col width="19.875" customWidth="1" style="1" min="3588" max="3588"/>
-    <col width="19" customWidth="1" style="1" min="3589" max="3589"/>
-    <col width="9" customWidth="1" style="1" min="3590" max="3840"/>
-    <col width="20.25" customWidth="1" style="1" min="3841" max="3841"/>
-    <col width="18.625" customWidth="1" style="1" min="3842" max="3842"/>
-    <col width="16.25" customWidth="1" style="1" min="3843" max="3843"/>
-    <col width="19.875" customWidth="1" style="1" min="3844" max="3844"/>
-    <col width="19" customWidth="1" style="1" min="3845" max="3845"/>
-    <col width="9" customWidth="1" style="1" min="3846" max="4096"/>
-    <col width="20.25" customWidth="1" style="1" min="4097" max="4097"/>
-    <col width="18.625" customWidth="1" style="1" min="4098" max="4098"/>
-    <col width="16.25" customWidth="1" style="1" min="4099" max="4099"/>
-    <col width="19.875" customWidth="1" style="1" min="4100" max="4100"/>
-    <col width="19" customWidth="1" style="1" min="4101" max="4101"/>
-    <col width="9" customWidth="1" style="1" min="4102" max="4352"/>
-    <col width="20.25" customWidth="1" style="1" min="4353" max="4353"/>
-    <col width="18.625" customWidth="1" style="1" min="4354" max="4354"/>
-    <col width="16.25" customWidth="1" style="1" min="4355" max="4355"/>
-    <col width="19.875" customWidth="1" style="1" min="4356" max="4356"/>
-    <col width="19" customWidth="1" style="1" min="4357" max="4357"/>
-    <col width="9" customWidth="1" style="1" min="4358" max="4608"/>
-    <col width="20.25" customWidth="1" style="1" min="4609" max="4609"/>
-    <col width="18.625" customWidth="1" style="1" min="4610" max="4610"/>
-    <col width="16.25" customWidth="1" style="1" min="4611" max="4611"/>
-    <col width="19.875" customWidth="1" style="1" min="4612" max="4612"/>
-    <col width="19" customWidth="1" style="1" min="4613" max="4613"/>
-    <col width="9" customWidth="1" style="1" min="4614" max="4864"/>
-    <col width="20.25" customWidth="1" style="1" min="4865" max="4865"/>
-    <col width="18.625" customWidth="1" style="1" min="4866" max="4866"/>
-    <col width="16.25" customWidth="1" style="1" min="4867" max="4867"/>
-    <col width="19.875" customWidth="1" style="1" min="4868" max="4868"/>
-    <col width="19" customWidth="1" style="1" min="4869" max="4869"/>
-    <col width="9" customWidth="1" style="1" min="4870" max="5120"/>
-    <col width="20.25" customWidth="1" style="1" min="5121" max="5121"/>
-    <col width="18.625" customWidth="1" style="1" min="5122" max="5122"/>
-    <col width="16.25" customWidth="1" style="1" min="5123" max="5123"/>
-    <col width="19.875" customWidth="1" style="1" min="5124" max="5124"/>
-    <col width="19" customWidth="1" style="1" min="5125" max="5125"/>
-    <col width="9" customWidth="1" style="1" min="5126" max="5376"/>
-    <col width="20.25" customWidth="1" style="1" min="5377" max="5377"/>
-    <col width="18.625" customWidth="1" style="1" min="5378" max="5378"/>
-    <col width="16.25" customWidth="1" style="1" min="5379" max="5379"/>
-    <col width="19.875" customWidth="1" style="1" min="5380" max="5380"/>
-    <col width="19" customWidth="1" style="1" min="5381" max="5381"/>
-    <col width="9" customWidth="1" style="1" min="5382" max="5632"/>
-    <col width="20.25" customWidth="1" style="1" min="5633" max="5633"/>
-    <col width="18.625" customWidth="1" style="1" min="5634" max="5634"/>
-    <col width="16.25" customWidth="1" style="1" min="5635" max="5635"/>
-    <col width="19.875" customWidth="1" style="1" min="5636" max="5636"/>
-    <col width="19" customWidth="1" style="1" min="5637" max="5637"/>
-    <col width="9" customWidth="1" style="1" min="5638" max="5888"/>
-    <col width="20.25" customWidth="1" style="1" min="5889" max="5889"/>
-    <col width="18.625" customWidth="1" style="1" min="5890" max="5890"/>
-    <col width="16.25" customWidth="1" style="1" min="5891" max="5891"/>
-    <col width="19.875" customWidth="1" style="1" min="5892" max="5892"/>
-    <col width="19" customWidth="1" style="1" min="5893" max="5893"/>
-    <col width="9" customWidth="1" style="1" min="5894" max="6144"/>
-    <col width="20.25" customWidth="1" style="1" min="6145" max="6145"/>
-    <col width="18.625" customWidth="1" style="1" min="6146" max="6146"/>
-    <col width="16.25" customWidth="1" style="1" min="6147" max="6147"/>
-    <col width="19.875" customWidth="1" style="1" min="6148" max="6148"/>
-    <col width="19" customWidth="1" style="1" min="6149" max="6149"/>
-    <col width="9" customWidth="1" style="1" min="6150" max="6400"/>
-    <col width="20.25" customWidth="1" style="1" min="6401" max="6401"/>
-    <col width="18.625" customWidth="1" style="1" min="6402" max="6402"/>
-    <col width="16.25" customWidth="1" style="1" min="6403" max="6403"/>
-    <col width="19.875" customWidth="1" style="1" min="6404" max="6404"/>
-    <col width="19" customWidth="1" style="1" min="6405" max="6405"/>
-    <col width="9" customWidth="1" style="1" min="6406" max="6656"/>
-    <col width="20.25" customWidth="1" style="1" min="6657" max="6657"/>
-    <col width="18.625" customWidth="1" style="1" min="6658" max="6658"/>
-    <col width="16.25" customWidth="1" style="1" min="6659" max="6659"/>
-    <col width="19.875" customWidth="1" style="1" min="6660" max="6660"/>
-    <col width="19" customWidth="1" style="1" min="6661" max="6661"/>
-    <col width="9" customWidth="1" style="1" min="6662" max="6912"/>
-    <col width="20.25" customWidth="1" style="1" min="6913" max="6913"/>
-    <col width="18.625" customWidth="1" style="1" min="6914" max="6914"/>
-    <col width="16.25" customWidth="1" style="1" min="6915" max="6915"/>
-    <col width="19.875" customWidth="1" style="1" min="6916" max="6916"/>
-    <col width="19" customWidth="1" style="1" min="6917" max="6917"/>
-    <col width="9" customWidth="1" style="1" min="6918" max="7168"/>
-    <col width="20.25" customWidth="1" style="1" min="7169" max="7169"/>
-    <col width="18.625" customWidth="1" style="1" min="7170" max="7170"/>
-    <col width="16.25" customWidth="1" style="1" min="7171" max="7171"/>
-    <col width="19.875" customWidth="1" style="1" min="7172" max="7172"/>
-    <col width="19" customWidth="1" style="1" min="7173" max="7173"/>
-    <col width="9" customWidth="1" style="1" min="7174" max="7424"/>
-    <col width="20.25" customWidth="1" style="1" min="7425" max="7425"/>
-    <col width="18.625" customWidth="1" style="1" min="7426" max="7426"/>
-    <col width="16.25" customWidth="1" style="1" min="7427" max="7427"/>
-    <col width="19.875" customWidth="1" style="1" min="7428" max="7428"/>
-    <col width="19" customWidth="1" style="1" min="7429" max="7429"/>
-    <col width="9" customWidth="1" style="1" min="7430" max="7680"/>
-    <col width="20.25" customWidth="1" style="1" min="7681" max="7681"/>
-    <col width="18.625" customWidth="1" style="1" min="7682" max="7682"/>
-    <col width="16.25" customWidth="1" style="1" min="7683" max="7683"/>
-    <col width="19.875" customWidth="1" style="1" min="7684" max="7684"/>
-    <col width="19" customWidth="1" style="1" min="7685" max="7685"/>
-    <col width="9" customWidth="1" style="1" min="7686" max="7936"/>
-    <col width="20.25" customWidth="1" style="1" min="7937" max="7937"/>
-    <col width="18.625" customWidth="1" style="1" min="7938" max="7938"/>
-    <col width="16.25" customWidth="1" style="1" min="7939" max="7939"/>
-    <col width="19.875" customWidth="1" style="1" min="7940" max="7940"/>
-    <col width="19" customWidth="1" style="1" min="7941" max="7941"/>
-    <col width="9" customWidth="1" style="1" min="7942" max="8192"/>
-    <col width="20.25" customWidth="1" style="1" min="8193" max="8193"/>
-    <col width="18.625" customWidth="1" style="1" min="8194" max="8194"/>
-    <col width="16.25" customWidth="1" style="1" min="8195" max="8195"/>
-    <col width="19.875" customWidth="1" style="1" min="8196" max="8196"/>
-    <col width="19" customWidth="1" style="1" min="8197" max="8197"/>
-    <col width="9" customWidth="1" style="1" min="8198" max="8448"/>
-    <col width="20.25" customWidth="1" style="1" min="8449" max="8449"/>
-    <col width="18.625" customWidth="1" style="1" min="8450" max="8450"/>
-    <col width="16.25" customWidth="1" style="1" min="8451" max="8451"/>
-    <col width="19.875" customWidth="1" style="1" min="8452" max="8452"/>
-    <col width="19" customWidth="1" style="1" min="8453" max="8453"/>
-    <col width="9" customWidth="1" style="1" min="8454" max="8704"/>
-    <col width="20.25" customWidth="1" style="1" min="8705" max="8705"/>
-    <col width="18.625" customWidth="1" style="1" min="8706" max="8706"/>
-    <col width="16.25" customWidth="1" style="1" min="8707" max="8707"/>
-    <col width="19.875" customWidth="1" style="1" min="8708" max="8708"/>
-    <col width="19" customWidth="1" style="1" min="8709" max="8709"/>
-    <col width="9" customWidth="1" style="1" min="8710" max="8960"/>
-    <col width="20.25" customWidth="1" style="1" min="8961" max="8961"/>
-    <col width="18.625" customWidth="1" style="1" min="8962" max="8962"/>
-    <col width="16.25" customWidth="1" style="1" min="8963" max="8963"/>
-    <col width="19.875" customWidth="1" style="1" min="8964" max="8964"/>
-    <col width="19" customWidth="1" style="1" min="8965" max="8965"/>
-    <col width="9" customWidth="1" style="1" min="8966" max="9216"/>
-    <col width="20.25" customWidth="1" style="1" min="9217" max="9217"/>
-    <col width="18.625" customWidth="1" style="1" min="9218" max="9218"/>
-    <col width="16.25" customWidth="1" style="1" min="9219" max="9219"/>
-    <col width="19.875" customWidth="1" style="1" min="9220" max="9220"/>
-    <col width="19" customWidth="1" style="1" min="9221" max="9221"/>
-    <col width="9" customWidth="1" style="1" min="9222" max="9472"/>
-    <col width="20.25" customWidth="1" style="1" min="9473" max="9473"/>
-    <col width="18.625" customWidth="1" style="1" min="9474" max="9474"/>
-    <col width="16.25" customWidth="1" style="1" min="9475" max="9475"/>
-    <col width="19.875" customWidth="1" style="1" min="9476" max="9476"/>
-    <col width="19" customWidth="1" style="1" min="9477" max="9477"/>
-    <col width="9" customWidth="1" style="1" min="9478" max="9728"/>
-    <col width="20.25" customWidth="1" style="1" min="9729" max="9729"/>
-    <col width="18.625" customWidth="1" style="1" min="9730" max="9730"/>
-    <col width="16.25" customWidth="1" style="1" min="9731" max="9731"/>
-    <col width="19.875" customWidth="1" style="1" min="9732" max="9732"/>
-    <col width="19" customWidth="1" style="1" min="9733" max="9733"/>
-    <col width="9" customWidth="1" style="1" min="9734" max="9984"/>
-    <col width="20.25" customWidth="1" style="1" min="9985" max="9985"/>
-    <col width="18.625" customWidth="1" style="1" min="9986" max="9986"/>
-    <col width="16.25" customWidth="1" style="1" min="9987" max="9987"/>
-    <col width="19.875" customWidth="1" style="1" min="9988" max="9988"/>
-    <col width="19" customWidth="1" style="1" min="9989" max="9989"/>
-    <col width="9" customWidth="1" style="1" min="9990" max="10240"/>
-    <col width="20.25" customWidth="1" style="1" min="10241" max="10241"/>
-    <col width="18.625" customWidth="1" style="1" min="10242" max="10242"/>
-    <col width="16.25" customWidth="1" style="1" min="10243" max="10243"/>
-    <col width="19.875" customWidth="1" style="1" min="10244" max="10244"/>
-    <col width="19" customWidth="1" style="1" min="10245" max="10245"/>
-    <col width="9" customWidth="1" style="1" min="10246" max="10496"/>
-    <col width="20.25" customWidth="1" style="1" min="10497" max="10497"/>
-    <col width="18.625" customWidth="1" style="1" min="10498" max="10498"/>
-    <col width="16.25" customWidth="1" style="1" min="10499" max="10499"/>
-    <col width="19.875" customWidth="1" style="1" min="10500" max="10500"/>
-    <col width="19" customWidth="1" style="1" min="10501" max="10501"/>
-    <col width="9" customWidth="1" style="1" min="10502" max="10752"/>
-    <col width="20.25" customWidth="1" style="1" min="10753" max="10753"/>
-    <col width="18.625" customWidth="1" style="1" min="10754" max="10754"/>
-    <col width="16.25" customWidth="1" style="1" min="10755" max="10755"/>
-    <col width="19.875" customWidth="1" style="1" min="10756" max="10756"/>
-    <col width="19" customWidth="1" style="1" min="10757" max="10757"/>
-    <col width="9" customWidth="1" style="1" min="10758" max="11008"/>
-    <col width="20.25" customWidth="1" style="1" min="11009" max="11009"/>
-    <col width="18.625" customWidth="1" style="1" min="11010" max="11010"/>
-    <col width="16.25" customWidth="1" style="1" min="11011" max="11011"/>
-    <col width="19.875" customWidth="1" style="1" min="11012" max="11012"/>
-    <col width="19" customWidth="1" style="1" min="11013" max="11013"/>
-    <col width="9" customWidth="1" style="1" min="11014" max="11264"/>
-    <col width="20.25" customWidth="1" style="1" min="11265" max="11265"/>
-    <col width="18.625" customWidth="1" style="1" min="11266" max="11266"/>
-    <col width="16.25" customWidth="1" style="1" min="11267" max="11267"/>
-    <col width="19.875" customWidth="1" style="1" min="11268" max="11268"/>
-    <col width="19" customWidth="1" style="1" min="11269" max="11269"/>
-    <col width="9" customWidth="1" style="1" min="11270" max="11520"/>
-    <col width="20.25" customWidth="1" style="1" min="11521" max="11521"/>
-    <col width="18.625" customWidth="1" style="1" min="11522" max="11522"/>
-    <col width="16.25" customWidth="1" style="1" min="11523" max="11523"/>
-    <col width="19.875" customWidth="1" style="1" min="11524" max="11524"/>
-    <col width="19" customWidth="1" style="1" min="11525" max="11525"/>
-    <col width="9" customWidth="1" style="1" min="11526" max="11776"/>
-    <col width="20.25" customWidth="1" style="1" min="11777" max="11777"/>
-    <col width="18.625" customWidth="1" style="1" min="11778" max="11778"/>
-    <col width="16.25" customWidth="1" style="1" min="11779" max="11779"/>
-    <col width="19.875" customWidth="1" style="1" min="11780" max="11780"/>
-    <col width="19" customWidth="1" style="1" min="11781" max="11781"/>
-    <col width="9" customWidth="1" style="1" min="11782" max="12032"/>
-    <col width="20.25" customWidth="1" style="1" min="12033" max="12033"/>
-    <col width="18.625" customWidth="1" style="1" min="12034" max="12034"/>
-    <col width="16.25" customWidth="1" style="1" min="12035" max="12035"/>
-    <col width="19.875" customWidth="1" style="1" min="12036" max="12036"/>
-    <col width="19" customWidth="1" style="1" min="12037" max="12037"/>
-    <col width="9" customWidth="1" style="1" min="12038" max="12288"/>
-    <col width="20.25" customWidth="1" style="1" min="12289" max="12289"/>
-    <col width="18.625" customWidth="1" style="1" min="12290" max="12290"/>
-    <col width="16.25" customWidth="1" style="1" min="12291" max="12291"/>
-    <col width="19.875" customWidth="1" style="1" min="12292" max="12292"/>
-    <col width="19" customWidth="1" style="1" min="12293" max="12293"/>
-    <col width="9" customWidth="1" style="1" min="12294" max="12544"/>
-    <col width="20.25" customWidth="1" style="1" min="12545" max="12545"/>
-    <col width="18.625" customWidth="1" style="1" min="12546" max="12546"/>
-    <col width="16.25" customWidth="1" style="1" min="12547" max="12547"/>
-    <col width="19.875" customWidth="1" style="1" min="12548" max="12548"/>
-    <col width="19" customWidth="1" style="1" min="12549" max="12549"/>
-    <col width="9" customWidth="1" style="1" min="12550" max="12800"/>
-    <col width="20.25" customWidth="1" style="1" min="12801" max="12801"/>
-    <col width="18.625" customWidth="1" style="1" min="12802" max="12802"/>
-    <col width="16.25" customWidth="1" style="1" min="12803" max="12803"/>
-    <col width="19.875" customWidth="1" style="1" min="12804" max="12804"/>
-    <col width="19" customWidth="1" style="1" min="12805" max="12805"/>
-    <col width="9" customWidth="1" style="1" min="12806" max="13056"/>
-    <col width="20.25" customWidth="1" style="1" min="13057" max="13057"/>
-    <col width="18.625" customWidth="1" style="1" min="13058" max="13058"/>
-    <col width="16.25" customWidth="1" style="1" min="13059" max="13059"/>
-    <col width="19.875" customWidth="1" style="1" min="13060" max="13060"/>
-    <col width="19" customWidth="1" style="1" min="13061" max="13061"/>
-    <col width="9" customWidth="1" style="1" min="13062" max="13312"/>
-    <col width="20.25" customWidth="1" style="1" min="13313" max="13313"/>
-    <col width="18.625" customWidth="1" style="1" min="13314" max="13314"/>
-    <col width="16.25" customWidth="1" style="1" min="13315" max="13315"/>
-    <col width="19.875" customWidth="1" style="1" min="13316" max="13316"/>
-    <col width="19" customWidth="1" style="1" min="13317" max="13317"/>
-    <col width="9" customWidth="1" style="1" min="13318" max="13568"/>
-    <col width="20.25" customWidth="1" style="1" min="13569" max="13569"/>
-    <col width="18.625" customWidth="1" style="1" min="13570" max="13570"/>
-    <col width="16.25" customWidth="1" style="1" min="13571" max="13571"/>
-    <col width="19.875" customWidth="1" style="1" min="13572" max="13572"/>
-    <col width="19" customWidth="1" style="1" min="13573" max="13573"/>
-    <col width="9" customWidth="1" style="1" min="13574" max="13824"/>
-    <col width="20.25" customWidth="1" style="1" min="13825" max="13825"/>
-    <col width="18.625" customWidth="1" style="1" min="13826" max="13826"/>
-    <col width="16.25" customWidth="1" style="1" min="13827" max="13827"/>
-    <col width="19.875" customWidth="1" style="1" min="13828" max="13828"/>
-    <col width="19" customWidth="1" style="1" min="13829" max="13829"/>
-    <col width="9" customWidth="1" style="1" min="13830" max="14080"/>
-    <col width="20.25" customWidth="1" style="1" min="14081" max="14081"/>
-    <col width="18.625" customWidth="1" style="1" min="14082" max="14082"/>
-    <col width="16.25" customWidth="1" style="1" min="14083" max="14083"/>
-    <col width="19.875" customWidth="1" style="1" min="14084" max="14084"/>
-    <col width="19" customWidth="1" style="1" min="14085" max="14085"/>
-    <col width="9" customWidth="1" style="1" min="14086" max="14336"/>
-    <col width="20.25" customWidth="1" style="1" min="14337" max="14337"/>
-    <col width="18.625" customWidth="1" style="1" min="14338" max="14338"/>
-    <col width="16.25" customWidth="1" style="1" min="14339" max="14339"/>
-    <col width="19.875" customWidth="1" style="1" min="14340" max="14340"/>
-    <col width="19" customWidth="1" style="1" min="14341" max="14341"/>
-    <col width="9" customWidth="1" style="1" min="14342" max="14592"/>
-    <col width="20.25" customWidth="1" style="1" min="14593" max="14593"/>
-    <col width="18.625" customWidth="1" style="1" min="14594" max="14594"/>
-    <col width="16.25" customWidth="1" style="1" min="14595" max="14595"/>
-    <col width="19.875" customWidth="1" style="1" min="14596" max="14596"/>
-    <col width="19" customWidth="1" style="1" min="14597" max="14597"/>
-    <col width="9" customWidth="1" style="1" min="14598" max="14848"/>
-    <col width="20.25" customWidth="1" style="1" min="14849" max="14849"/>
-    <col width="18.625" customWidth="1" style="1" min="14850" max="14850"/>
-    <col width="16.25" customWidth="1" style="1" min="14851" max="14851"/>
-    <col width="19.875" customWidth="1" style="1" min="14852" max="14852"/>
-    <col width="19" customWidth="1" style="1" min="14853" max="14853"/>
-    <col width="9" customWidth="1" style="1" min="14854" max="15104"/>
-    <col width="20.25" customWidth="1" style="1" min="15105" max="15105"/>
-    <col width="18.625" customWidth="1" style="1" min="15106" max="15106"/>
-    <col width="16.25" customWidth="1" style="1" min="15107" max="15107"/>
-    <col width="19.875" customWidth="1" style="1" min="15108" max="15108"/>
-    <col width="19" customWidth="1" style="1" min="15109" max="15109"/>
-    <col width="9" customWidth="1" style="1" min="15110" max="15360"/>
-    <col width="20.25" customWidth="1" style="1" min="15361" max="15361"/>
-    <col width="18.625" customWidth="1" style="1" min="15362" max="15362"/>
-    <col width="16.25" customWidth="1" style="1" min="15363" max="15363"/>
-    <col width="19.875" customWidth="1" style="1" min="15364" max="15364"/>
-    <col width="19" customWidth="1" style="1" min="15365" max="15365"/>
-    <col width="9" customWidth="1" style="1" min="15366" max="15616"/>
-    <col width="20.25" customWidth="1" style="1" min="15617" max="15617"/>
-    <col width="18.625" customWidth="1" style="1" min="15618" max="15618"/>
-    <col width="16.25" customWidth="1" style="1" min="15619" max="15619"/>
-    <col width="19.875" customWidth="1" style="1" min="15620" max="15620"/>
-    <col width="19" customWidth="1" style="1" min="15621" max="15621"/>
-    <col width="9" customWidth="1" style="1" min="15622" max="15872"/>
-    <col width="20.25" customWidth="1" style="1" min="15873" max="15873"/>
-    <col width="18.625" customWidth="1" style="1" min="15874" max="15874"/>
-    <col width="16.25" customWidth="1" style="1" min="15875" max="15875"/>
-    <col width="19.875" customWidth="1" style="1" min="15876" max="15876"/>
-    <col width="19" customWidth="1" style="1" min="15877" max="15877"/>
-    <col width="9" customWidth="1" style="1" min="15878" max="16128"/>
-    <col width="20.25" customWidth="1" style="1" min="16129" max="16129"/>
-    <col width="18.625" customWidth="1" style="1" min="16130" max="16130"/>
-    <col width="16.25" customWidth="1" style="1" min="16131" max="16131"/>
-    <col width="19.875" customWidth="1" style="1" min="16132" max="16132"/>
-    <col width="19" customWidth="1" style="1" min="16133" max="16133"/>
-    <col width="9" customWidth="1" style="1" min="16134" max="16384"/>
+    <col width="9" customWidth="1" style="1" min="9" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="38.25" customHeight="1" s="44">

--- a/resources/templates/system/deregistration_contract.xlsx
+++ b/resources/templates/system/deregistration_contract.xlsx
@@ -25,22 +25,22 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">export 2 area 194-75 Okryendong Yeonsugu incheon  Korea  </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">63 sunghyeonro ilsandonggu Kyeonggydo  Korea</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">TEL : 82 -10-9009-9977</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">FAX : 82 - 031 - 499 - 1989</t>
+      <t xml:space="preserve">163 Sangidaehak-ro, Siheung-si,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Gyeonggi-do, Republic of Korea</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">TEL : 82-505-355-9977</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">FAX : 82-505-366-9977</t>
     </r>
   </si>
   <si>
@@ -1281,7 +1281,7 @@
       <c r="A2" s="33" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">export 2 area 194-75 Okryendong Yeonsugu incheon  Korea  </t>
+            <t xml:space="preserve">163 Sangidaehak-ro, Siheung-si,</t>
           </r>
         </is>
       </c>
@@ -1290,7 +1290,7 @@
       <c r="A3" s="33" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">63 sunghyeonro ilsandonggu Kyeonggydo  Korea</t>
+            <t xml:space="preserve">Gyeonggi-do, Republic of Korea</t>
           </r>
         </is>
       </c>
@@ -1303,7 +1303,7 @@
       <c r="E4" s="5" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">TEL : 82 -10-9009-9977</t>
+            <t xml:space="preserve">TEL : 82-505-355-9977</t>
           </r>
         </is>
       </c>
@@ -1316,7 +1316,7 @@
       <c r="E5" s="5" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">FAX : 82 - 031 - 499 - 1989</t>
+            <t xml:space="preserve">FAX : 82-505-366-9977</t>
           </r>
         </is>
       </c>
